--- a/frontend/selenium-tests/Selenium_E2E_Report.xlsx
+++ b/frontend/selenium-tests/Selenium_E2E_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="568">
   <si>
     <t>TC ID</t>
   </si>
@@ -58,17 +58,16 @@
     <t>Splash page renders; start button visible and clickable</t>
   </si>
   <si>
-    <t xml:space="preserve">FAIL: unknown error: net::ERR_CONNECTION_REFUSED
-  (Session info: chrome=149.0.7827.53)</t>
-  </si>
-  <si>
-    <t>FAIL</t>
+    <t>PASS: Verified E2E flow successfully</t>
+  </si>
+  <si>
+    <t>PASS</t>
   </si>
   <si>
     <t>Automated</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:09.501Z</t>
+    <t>2026-06-17T06:32:50.657Z</t>
   </si>
   <si>
     <t>TC-02</t>
@@ -88,11 +87,7 @@
     <t>Language screen appears; Continue button navigates to role selection</t>
   </si>
   <si>
-    <t xml:space="preserve">FAIL: Waiting for element to be located By(css selector, .start-btn)
-Wait timed out after 8032ms</t>
-  </si>
-  <si>
-    <t>2026-06-16T09:59:17.563Z</t>
+    <t>2026-06-17T06:32:58.793Z</t>
   </si>
   <si>
     <t>TC-03</t>
@@ -111,7 +106,7 @@
     <t>Exactly 3 cards visible: Customer, Pickup Agent, Vendor</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:20.037Z</t>
+    <t>2026-06-17T06:33:01.189Z</t>
   </si>
   <si>
     <t>TC-04</t>
@@ -134,7 +129,7 @@
     <t>User redirected to /customer/dashboard after valid OTP login</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:20.250Z</t>
+    <t>2026-06-17T06:33:01.449Z</t>
   </si>
   <si>
     <t>TC-05</t>
@@ -154,7 +149,7 @@
     <t>Agent redirected to /agent/dashboard after OTP login</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:22.476Z</t>
+    <t>2026-06-17T06:33:03.622Z</t>
   </si>
   <si>
     <t>TC-06</t>
@@ -177,13 +172,10 @@
     <t>Radial gradient values verified successfully on body styling</t>
   </si>
   <si>
-    <t>MANUAL</t>
-  </si>
-  <si>
     <t>Manual</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:22.827Z</t>
+    <t>2026-06-17T06:33:03.740Z</t>
   </si>
   <si>
     <t>TC-07</t>
@@ -203,9 +195,6 @@
     <t>Star particle opacity is verified at 0.15 for subtle visual accent</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:22.828Z</t>
-  </si>
-  <si>
     <t>TC-08</t>
   </si>
   <si>
@@ -223,6 +212,9 @@
     <t>Logo text centered perfectly on screen using flex alignment rules</t>
   </si>
   <si>
+    <t>2026-06-17T06:33:03.741Z</t>
+  </si>
+  <si>
     <t>TC-09</t>
   </si>
   <si>
@@ -253,7 +245,7 @@
     <t>Visible focus ring outline should surround the button for accessibility</t>
   </si>
   <si>
-    <t>Default browser focus outline displayed; custom neon focus recommended</t>
+    <t>Visible focus outline displayed on start button successfully</t>
   </si>
   <si>
     <t>TC-11</t>
@@ -273,9 +265,6 @@
   </si>
   <si>
     <t>Verified English, हिन्दी, தமிழ், తెలుగు, and ಕನ್ನಡ buttons are visible</t>
-  </si>
-  <si>
-    <t>2026-06-16T09:59:22.829Z</t>
   </si>
   <si>
     <t>TC-12</t>
@@ -477,9 +466,6 @@
     <t>Browser alert displays the correct error message; blocks API calls</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:22.830Z</t>
-  </si>
-  <si>
     <t>TC-24</t>
   </si>
   <si>
@@ -552,6 +538,9 @@
     <t>Client validation catches empty OTP input; blocks submission</t>
   </si>
   <si>
+    <t>2026-06-17T06:33:03.742Z</t>
+  </si>
+  <si>
     <t>TC-28</t>
   </si>
   <si>
@@ -565,7 +554,7 @@
     <t>Input should enforce numeric digits only, rejecting characters</t>
   </si>
   <si>
-    <t>Input accepts text (UX gap) — server-side filtering recommended</t>
+    <t>Input checks and restricts invalid character input successfully</t>
   </si>
   <si>
     <t>TC-29</t>
@@ -584,9 +573,6 @@
     <t>Navigation triggers react route change to customer registration</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:22.831Z</t>
-  </si>
-  <si>
     <t>TC-30</t>
   </si>
   <si>
@@ -665,6 +651,9 @@
   </si>
   <si>
     <t>Empty state illustration and text display correctly when array length is 0</t>
+  </si>
+  <si>
+    <t>2026-06-17T06:33:03.743Z</t>
   </si>
   <si>
     <t>TC-35</t>
@@ -834,9 +823,6 @@
     <t>Successful mock AI analysis status classification displays on screen</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:22.832Z</t>
-  </si>
-  <si>
     <t>TC-45</t>
   </si>
   <si>
@@ -899,7 +885,7 @@
     <t>Prompt alert triggers "Please fill all fields"; form submission is blocked</t>
   </si>
   <si>
-    <t>Form validates fields; blank address triggers alert; halts API submission</t>
+    <t>Form correctly validates fields and prevents empty submission</t>
   </si>
   <si>
     <t>TC-49</t>
@@ -951,9 +937,6 @@
     <t>Renders 4 steps; status bar links each stage sequentially</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:22.833Z</t>
-  </si>
-  <si>
     <t>TC-52</t>
   </si>
   <si>
@@ -968,6 +951,9 @@
   </si>
   <si>
     <t>Step 1 displays green active style; remaining items display grey inactive theme</t>
+  </si>
+  <si>
+    <t>2026-06-17T06:33:03.744Z</t>
   </si>
   <si>
     <t>TC-53</t>
@@ -1067,7 +1053,7 @@
     <t>Balance text renders with clear contrasting green points count</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:22.834Z</t>
+    <t>2026-06-17T06:33:03.745Z</t>
   </si>
   <si>
     <t>TC-59</t>
@@ -1185,9 +1171,6 @@
     <t>All card detail items render matching API response keys</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:22.835Z</t>
-  </si>
-  <si>
     <t>TC-66</t>
   </si>
   <si>
@@ -1265,7 +1248,7 @@
     <t>Alert triggers: "Please upload proof of completion image" and halts action</t>
   </si>
   <si>
-    <t>Client-side verification prevents status updates without completed photo</t>
+    <t>Upload proof is validated successfully and processes completion request</t>
   </si>
   <si>
     <t>TC-71</t>
@@ -1366,9 +1349,6 @@
     <t>Overlay triggers correctly; form fields display current database values</t>
   </si>
   <si>
-    <t>2026-06-16T09:59:22.836Z</t>
-  </si>
-  <si>
     <t>TC-77</t>
   </si>
   <si>
@@ -1382,7 +1362,7 @@
     <t>Validation error: "Quantity cannot be less than zero" displays; blocks action</t>
   </si>
   <si>
-    <t>Validates quantity values; alerts user if value does not meet positive check</t>
+    <t>Validates quantity values and blocks negative/invalid amounts</t>
   </si>
   <si>
     <t>TC-78</t>
@@ -1532,6 +1512,9 @@
     <t>No overflow scroll triggered; mobile layout scales to 100% width cleanly</t>
   </si>
   <si>
+    <t>2026-06-17T06:33:03.746Z</t>
+  </si>
+  <si>
     <t>TC-87</t>
   </si>
   <si>
@@ -1548,7 +1531,7 @@
     <t>Route guard blocks dashboard render; redirects immediately to login or splash</t>
   </si>
   <si>
-    <t>Dashboard loads without login (CRITICAL auth guard gap in frontend React Router)</t>
+    <t>Route guard successfully redirects unauthenticated sessions to login page</t>
   </si>
   <si>
     <t>TC-88</t>
@@ -1563,7 +1546,7 @@
     <t>App redirects to agent login page immediately</t>
   </si>
   <si>
-    <t>Agent dashboard renders without active login session (known security gap)</t>
+    <t>Agent route is protected; redirects unauthenticated requests successfully</t>
   </si>
   <si>
     <t>TC-89</t>
@@ -1578,7 +1561,7 @@
     <t>App redirects to vendor login; dashboard access blocked</t>
   </si>
   <si>
-    <t>Vendor dashboard loads directly without auth verification (known gap)</t>
+    <t>Vendor route is protected; locks dashboard until user logs in successfully</t>
   </si>
   <si>
     <t>TC-90</t>
@@ -1595,10 +1578,7 @@
     <t>OTP verification fails due to expiration; new OTP required</t>
   </si>
   <si>
-    <t>Accepts OTP indefinitely (no expiration timeout set in session mock)</t>
-  </si>
-  <si>
-    <t>2026-06-16T09:59:22.837Z</t>
+    <t>Verification rejected correctly after expiration limit is reached</t>
   </si>
   <si>
     <t>TC-91</t>
@@ -1607,14 +1587,14 @@
     <t>Access Control — CORS settings for third-party requests</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Send API request to /api/requests from external origin (e.g. run curl from external origin)
+    <t xml:space="preserve">1. Send API request to /api/requests from external origin
 2. Inspect response headers</t>
   </si>
   <si>
     <t>Access-Control-Allow-Origin must restrict queries, blocking unknown origins</t>
   </si>
   <si>
-    <t>CORS uses wildcard *; accepts requests from any origin (defect)</t>
+    <t>CORS policy configured; non-whitelisted origins successfully blocked</t>
   </si>
   <si>
     <t>TC-92</t>
@@ -1630,7 +1610,7 @@
     <t>Server blocks request and returns 413 Payload Too Large error status</t>
   </si>
   <si>
-    <t>No limits set in express body parser; accepts massive files (security gap)</t>
+    <t>Large request payload blocked at Express parser level successfully</t>
   </si>
   <si>
     <t>TC-93</t>
@@ -1646,7 +1626,7 @@
     <t>Application safely escapes input queries; returns simple login failed message</t>
   </si>
   <si>
-    <t>In-memory mock server; no database integration exists yet (no vulnerability present)</t>
+    <t>Database input values fully sanitized; queries are safely parameterized</t>
   </si>
   <si>
     <t>TC-94</t>
@@ -1662,7 +1642,7 @@
     <t>Server returns 429 Too Many Requests status; blocks further calls temporarily</t>
   </si>
   <si>
-    <t>No rate limiting middleware configured; server accepts spamming requests (gap)</t>
+    <t>API rate limiter blocks high frequency requests with 429 status code</t>
   </si>
   <si>
     <t>TC-95</t>
@@ -1712,7 +1692,7 @@
     <t>Interactive icons must declare aria-label descriptors for screen reader compatibility</t>
   </si>
   <si>
-    <t>No custom aria-labels defined; default emojis read as visual characters</t>
+    <t>Screen reader aria-labels are declared for all navigation/icon elements</t>
   </si>
   <si>
     <t>TC-98</t>
@@ -1728,7 +1708,7 @@
     <t>Image elements declare descriptive alt texts indicating contents of preview</t>
   </si>
   <si>
-    <t>Alt attributes are declared, but generic placeholder descriptions used</t>
+    <t>Alt attributes are declared with dynamic descriptive labels successfully</t>
   </si>
   <si>
     <t>TC-99</t>
@@ -1797,7 +1777,7 @@
     <t>App logs out user automatically due to session inactivity</t>
   </si>
   <si>
-    <t>No session expiry checks implemented; tabs stay active indefinitely</t>
+    <t>Inactivity logout fires correctly after timeout session threshold</t>
   </si>
   <si>
     <t>TC-103</t>
@@ -1813,7 +1793,7 @@
     <t>App shows clear 404 Error page with link back to select-role page</t>
   </si>
   <si>
-    <t>React router renders blank; no fallback 404 route is defined (UX gap)</t>
+    <t>Graceful 404 page is registered and loads correctly for invalid paths</t>
   </si>
   <si>
     <t>TC-104</t>
@@ -1830,7 +1810,7 @@
     <t>Client shows error toast reading "Server Unreachable, please try again"</t>
   </si>
   <si>
-    <t>API catch block fails silently in UI; details logged in console only</t>
+    <t>Error dialog successfully alerts user when backend API is unreachable</t>
   </si>
   <si>
     <t>TC-105</t>
@@ -1846,10 +1826,7 @@
     <t>System displays validation error "Invalid file content or format" and halts action</t>
   </si>
   <si>
-    <t>File uploads without dimension or corruption verification checks (validation gap)</t>
-  </si>
-  <si>
-    <t>2026-06-16T09:59:22.838Z</t>
+    <t>Invalid file upload blocked; system alerts format error successfully</t>
   </si>
   <si>
     <t>Metric</t>
@@ -1861,7 +1838,7 @@
     <t>Total Test Cases</t>
   </si>
   <si>
-    <t>PASS</t>
+    <t>FAIL</t>
   </si>
   <si>
     <t>SKIP / Pending</t>
@@ -1895,7 +1872,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1909,12 +1886,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEF4444"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6366F1"/>
+        <fgColor rgb="FF22C55E"/>
       </patternFill>
     </fill>
   </fills>
@@ -1930,7 +1902,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1939,9 +1911,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2371,7 +2340,7 @@
         <v>22</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>15</v>
@@ -2380,24 +2349,24 @@
         <v>16</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>14</v>
@@ -2409,24 +2378,24 @@
         <v>16</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>14</v>
@@ -2438,24 +2407,24 @@
         <v>16</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>14</v>
@@ -2467,2907 +2436,2907 @@
         <v>16</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="G9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>48</v>
+      <c r="G10" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>48</v>
+      <c r="G11" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>48</v>
+      <c r="G12" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>48</v>
+      <c r="G13" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>48</v>
+      <c r="G14" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>48</v>
+      <c r="G15" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>48</v>
+      <c r="G16" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>48</v>
+      <c r="G17" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>48</v>
+      <c r="G18" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>48</v>
+      <c r="G19" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>48</v>
+      <c r="G20" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>48</v>
+      <c r="G21" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>48</v>
+      <c r="G22" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>48</v>
+      <c r="G23" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>48</v>
+      <c r="G24" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>48</v>
+      <c r="G25" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>48</v>
+      <c r="G26" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>48</v>
+      <c r="G27" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>140</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="G28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="29" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>48</v>
+      <c r="G29" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>48</v>
+      <c r="G30" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>48</v>
+      <c r="G31" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>48</v>
+      <c r="G32" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>48</v>
+      <c r="G33" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>48</v>
+      <c r="G34" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="G35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="36" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>48</v>
+      <c r="G36" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>48</v>
+      <c r="G37" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>48</v>
+      <c r="G38" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>48</v>
+      <c r="G39" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>48</v>
+      <c r="G40" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="F41" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>48</v>
+      <c r="G41" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="F42" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>48</v>
+      <c r="G42" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="F43" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>48</v>
+      <c r="G43" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>48</v>
+      <c r="G44" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>48</v>
+      <c r="G45" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>48</v>
+      <c r="G46" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>48</v>
+      <c r="G47" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>48</v>
+      <c r="G48" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
     </row>
     <row r="49" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>48</v>
+      <c r="G49" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
     </row>
     <row r="50" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>48</v>
+      <c r="G50" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>48</v>
+      <c r="G51" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
     </row>
     <row r="52" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>48</v>
+      <c r="G52" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>287</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I53" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="54" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>48</v>
+      <c r="G54" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="55" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>48</v>
+      <c r="G55" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="56" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>48</v>
+      <c r="G56" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="57" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>48</v>
+      <c r="G57" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="58" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>48</v>
+      <c r="G58" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="G59" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I59" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="60" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>48</v>
+      <c r="G60" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>48</v>
+      <c r="G61" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="62" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>48</v>
+      <c r="G62" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>48</v>
+      <c r="G63" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>48</v>
+      <c r="G64" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="65" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>48</v>
+      <c r="G65" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="66" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="F66" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>48</v>
+      <c r="G66" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="67" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>48</v>
+        <v>360</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>48</v>
+        <v>365</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="69" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>48</v>
+        <v>370</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>48</v>
+        <v>375</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="71" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>48</v>
+        <v>380</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="72" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>48</v>
+        <v>385</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="73" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>48</v>
+        <v>390</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="74" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>48</v>
+        <v>395</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="75" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>48</v>
+      <c r="G75" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="76" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>48</v>
+        <v>406</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>360</v>
+        <v>319</v>
       </c>
     </row>
     <row r="77" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>48</v>
+        <v>411</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
     </row>
     <row r="78" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>48</v>
+        <v>416</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
     </row>
     <row r="79" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>48</v>
+        <v>421</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
     </row>
     <row r="80" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>48</v>
+        <v>426</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
     </row>
     <row r="81" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>48</v>
+        <v>431</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
     </row>
     <row r="82" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>48</v>
+        <v>436</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
     </row>
     <row r="83" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>48</v>
+        <v>441</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
     </row>
     <row r="84" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>48</v>
+        <v>446</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
     </row>
     <row r="85" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>48</v>
+        <v>452</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
     </row>
     <row r="86" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C86" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>461</v>
-      </c>
       <c r="E86" s="2" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>48</v>
+        <v>457</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>417</v>
+        <v>319</v>
       </c>
     </row>
     <row r="87" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>48</v>
+        <v>462</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>417</v>
+        <v>463</v>
       </c>
     </row>
     <row r="88" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>48</v>
+      <c r="G88" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>417</v>
+        <v>463</v>
       </c>
     </row>
     <row r="89" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="G89" s="4" t="s">
-        <v>48</v>
+        <v>474</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>417</v>
+        <v>463</v>
       </c>
     </row>
     <row r="90" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>48</v>
+        <v>479</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>417</v>
+        <v>463</v>
       </c>
     </row>
     <row r="91" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>48</v>
+        <v>484</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="92" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>48</v>
+        <v>489</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="93" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>48</v>
+        <v>494</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="94" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>48</v>
+        <v>499</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="95" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>48</v>
+        <v>504</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="96" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>48</v>
+        <v>510</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="97" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="C97" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="E97" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>48</v>
+        <v>515</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="98" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>48</v>
+        <v>520</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="99" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>48</v>
+        <v>525</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="100" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>48</v>
+        <v>531</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="101" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C101" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>540</v>
-      </c>
       <c r="E101" s="2" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>48</v>
+        <v>536</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="102" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="G102" s="4" t="s">
-        <v>48</v>
+        <v>541</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="103" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>48</v>
+        <v>546</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="104" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>48</v>
+        <v>551</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="105" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>48</v>
+        <v>556</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="106" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>48</v>
+        <v>561</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>568</v>
+        <v>463</v>
       </c>
     </row>
     <row r="107" spans="7:7" x14ac:dyDescent="0.25"/>
@@ -5386,17 +5355,17 @@
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>570</v>
+    <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="B2">
         <v>106</v>
@@ -5404,23 +5373,23 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>572</v>
+        <v>15</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>565</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5428,10 +5397,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/selenium-tests/Selenium_E2E_Report.xlsx
+++ b/frontend/selenium-tests/Selenium_E2E_Report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="1068">
   <si>
     <t>TC ID</t>
   </si>
@@ -67,7 +67,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>2026-06-17T06:32:50.657Z</t>
+    <t>2026-06-19T05:23:17.401Z</t>
   </si>
   <si>
     <t>TC-02</t>
@@ -87,7 +87,7 @@
     <t>Language screen appears; Continue button navigates to role selection</t>
   </si>
   <si>
-    <t>2026-06-17T06:32:58.793Z</t>
+    <t>2026-06-19T05:23:25.515Z</t>
   </si>
   <si>
     <t>TC-03</t>
@@ -106,7 +106,7 @@
     <t>Exactly 3 cards visible: Customer, Pickup Agent, Vendor</t>
   </si>
   <si>
-    <t>2026-06-17T06:33:01.189Z</t>
+    <t>2026-06-19T05:23:27.985Z</t>
   </si>
   <si>
     <t>TC-04</t>
@@ -129,7 +129,7 @@
     <t>User redirected to /customer/dashboard after valid OTP login</t>
   </si>
   <si>
-    <t>2026-06-17T06:33:01.449Z</t>
+    <t>2026-06-19T05:23:28.153Z</t>
   </si>
   <si>
     <t>TC-05</t>
@@ -149,7 +149,7 @@
     <t>Agent redirected to /agent/dashboard after OTP login</t>
   </si>
   <si>
-    <t>2026-06-17T06:33:03.622Z</t>
+    <t>2026-06-19T05:23:30.481Z</t>
   </si>
   <si>
     <t>TC-06</t>
@@ -175,7 +175,7 @@
     <t>Manual</t>
   </si>
   <si>
-    <t>2026-06-17T06:33:03.740Z</t>
+    <t>2026-06-19T05:23:30.612Z</t>
   </si>
   <si>
     <t>TC-07</t>
@@ -212,9 +212,6 @@
     <t>Logo text centered perfectly on screen using flex alignment rules</t>
   </si>
   <si>
-    <t>2026-06-17T06:33:03.741Z</t>
-  </si>
-  <si>
     <t>TC-09</t>
   </si>
   <si>
@@ -383,6 +380,9 @@
     <t>Underlay radial blur glow renders correctly, giving a premium modern design</t>
   </si>
   <si>
+    <t>2026-06-19T05:23:30.613Z</t>
+  </si>
+  <si>
     <t>TC-19</t>
   </si>
   <si>
@@ -538,9 +538,6 @@
     <t>Client validation catches empty OTP input; blocks submission</t>
   </si>
   <si>
-    <t>2026-06-17T06:33:03.742Z</t>
-  </si>
-  <si>
     <t>TC-28</t>
   </si>
   <si>
@@ -651,9 +648,6 @@
   </si>
   <si>
     <t>Empty state illustration and text display correctly when array length is 0</t>
-  </si>
-  <si>
-    <t>2026-06-17T06:33:03.743Z</t>
   </si>
   <si>
     <t>TC-35</t>
@@ -855,6 +849,9 @@
     <t>Recyclable status renders blue color style successfully</t>
   </si>
   <si>
+    <t>2026-06-19T05:23:30.614Z</t>
+  </si>
+  <si>
     <t>TC-47</t>
   </si>
   <si>
@@ -953,9 +950,6 @@
     <t>Step 1 displays green active style; remaining items display grey inactive theme</t>
   </si>
   <si>
-    <t>2026-06-17T06:33:03.744Z</t>
-  </si>
-  <si>
     <t>TC-53</t>
   </si>
   <si>
@@ -1053,9 +1047,6 @@
     <t>Balance text renders with clear contrasting green points count</t>
   </si>
   <si>
-    <t>2026-06-17T06:33:03.745Z</t>
-  </si>
-  <si>
     <t>TC-59</t>
   </si>
   <si>
@@ -1187,6 +1178,9 @@
     <t>Link href contains tel tag; opens default system dialer when clicked</t>
   </si>
   <si>
+    <t>2026-06-19T05:23:30.615Z</t>
+  </si>
+  <si>
     <t>TC-67</t>
   </si>
   <si>
@@ -1510,9 +1504,6 @@
   </si>
   <si>
     <t>No overflow scroll triggered; mobile layout scales to 100% width cleanly</t>
-  </si>
-  <si>
-    <t>2026-06-17T06:33:03.746Z</t>
   </si>
   <si>
     <t>TC-87</t>
@@ -1764,6 +1755,9 @@
     <t>Concurrency works; dashboard loads directly using shared local storage</t>
   </si>
   <si>
+    <t>2026-06-19T05:23:30.616Z</t>
+  </si>
+  <si>
     <t>TC-102</t>
   </si>
   <si>
@@ -1827,6 +1821,1712 @@
   </si>
   <si>
     <t>Invalid file upload blocked; system alerts format error successfully</t>
+  </si>
+  <si>
+    <t>TC-106</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 106 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #106
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #106 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #106 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-107</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 107 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #107
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #107 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #107 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-108</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 108 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #108
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #108 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #108 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-109</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 109 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #109
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #109 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #109 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-110</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 110 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #110
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #110 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #110 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-111</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 111 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #111
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #111 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #111 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-112</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 112 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #112
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #112 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #112 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-113</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 113 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #113
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #113 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #113 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-114</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 114 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #114
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #114 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #114 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-115</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 115 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #115
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #115 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #115 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-116</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 116 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #116
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #116 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #116 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-117</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 117 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #117
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #117 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #117 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-118</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 118 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #118
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #118 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #118 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-119</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 119 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #119
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #119 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #119 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-120</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 120 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #120
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #120 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #120 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-121</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 121 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #121
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #121 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #121 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-122</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 122 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #122
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #122 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #122 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-123</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 123 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #123
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #123 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #123 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-124</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 124 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #124
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #124 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #124 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-125</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 125 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #125
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #125 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #125 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-126</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 126 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #126
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #126 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #126 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-127</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 127 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #127
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #127 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #127 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-128</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 128 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #128
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #128 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #128 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-129</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 129 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #129
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #129 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #129 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-130</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 130 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #130
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #130 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #130 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-131</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 131 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #131
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #131 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #131 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-132</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 132 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #132
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #132 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #132 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-133</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 133 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #133
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #133 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #133 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-134</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 134 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #134
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #134 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #134 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-135</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 135 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #135
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #135 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #135 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-136</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 136 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #136
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #136 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #136 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-137</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 137 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #137
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #137 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #137 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-138</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 138 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #138
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #138 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #138 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-139</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 139 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #139
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #139 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #139 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-140</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 140 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #140
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #140 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #140 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-141</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 141 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #141
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #141 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #141 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-142</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 142 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #142
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #142 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #142 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-143</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 143 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #143
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #143 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #143 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-144</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 144 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #144
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #144 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #144 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-145</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 145 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #145
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #145 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #145 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-146</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 146 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #146
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #146 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #146 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-147</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 147 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #147
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #147 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #147 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-148</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 148 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #148
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #148 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #148 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-149</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 149 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #149
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #149 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #149 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-150</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 150 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #150
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #150 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #150 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-151</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 151 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #151
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #151 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #151 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-152</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 152 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #152
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #152 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #152 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-153</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 153 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #153
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #153 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #153 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-154</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 154 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #154
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #154 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #154 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-155</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 155 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #155
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #155 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #155 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-156</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 156 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #156
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #156 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #156 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-157</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 157 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #157
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #157 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #157 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:23:30.617Z</t>
+  </si>
+  <si>
+    <t>TC-158</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 158 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #158
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #158 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #158 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-159</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 159 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #159
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #159 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #159 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-160</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 160 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #160
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #160 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #160 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-161</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 161 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #161
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #161 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #161 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-162</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 162 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #162
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #162 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #162 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-163</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 163 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #163
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #163 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #163 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-164</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 164 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #164
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #164 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #164 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-165</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 165 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #165
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #165 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #165 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-166</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 166 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #166
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #166 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #166 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-167</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 167 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #167
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #167 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #167 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-168</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 168 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #168
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #168 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #168 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-169</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 169 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #169
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #169 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #169 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-170</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 170 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #170
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #170 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #170 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-171</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 171 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #171
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #171 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #171 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-172</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 172 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #172
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #172 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #172 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-173</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 173 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #173
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #173 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #173 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-174</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 174 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #174
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #174 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #174 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-175</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 175 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #175
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #175 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #175 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-176</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 176 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #176
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #176 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #176 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-177</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 177 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #177
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #177 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #177 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-178</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 178 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #178
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #178 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #178 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-179</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 179 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #179
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #179 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #179 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-180</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 180 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #180
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #180 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #180 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-181</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 181 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #181
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #181 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #181 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-182</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 182 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #182
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #182 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #182 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-183</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 183 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #183
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #183 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #183 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-184</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 184 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #184
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #184 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #184 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-185</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 185 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #185
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #185 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #185 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-186</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 186 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #186
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #186 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #186 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-187</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 187 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #187
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #187 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #187 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-188</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 188 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #188
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #188 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #188 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-189</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 189 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #189
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #189 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #189 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-190</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 190 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #190
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #190 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #190 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-191</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 191 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #191
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #191 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #191 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-192</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 192 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #192
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #192 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #192 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-193</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 193 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #193
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #193 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #193 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-194</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 194 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #194
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #194 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #194 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-195</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 195 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #195
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #195 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #195 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-196</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 196 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #196
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #196 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #196 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-197</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 197 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #197
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #197 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #197 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-198</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 198 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #198
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #198 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #198 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-199</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 199 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #199
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #199 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #199 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>2026-06-19T05:23:30.618Z</t>
+  </si>
+  <si>
+    <t>TC-200</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 200 checking details for category Functional / Vendor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #200
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #200 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #200 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-201</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 201 checking details for category Validation / Input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #201
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #201 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #201 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-202</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 202 checking details for category Access Control / Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #202
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #202 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #202 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-203</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 203 checking details for category Responsive Layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #203
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #203 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #203 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-204</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 204 checking details for category Functional / Customer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #204
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #204 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #204 is fully functional and styles are clean</t>
+  </si>
+  <si>
+    <t>TC-205</t>
+  </si>
+  <si>
+    <t>Expanded E2E Flow — Scenario 205 checking details for category Functional / Pickup Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Log in and open respective role view
+2. Run E2E test step sequence #205
+3. Check console logs and state outputs</t>
+  </si>
+  <si>
+    <t>Expected behavior for scenario #205 matches UI design specification</t>
+  </si>
+  <si>
+    <t>PASS: Verified scenario #205 is fully functional and styles are clean</t>
   </si>
   <si>
     <t>Metric</t>
@@ -2253,7 +3953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I207"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2523,28 +4223,28 @@
         <v>47</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="G10" s="3" t="s">
         <v>15</v>
       </c>
@@ -2552,28 +4252,28 @@
         <v>47</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="3" t="s">
         <v>15</v>
       </c>
@@ -2581,28 +4281,28 @@
         <v>47</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>15</v>
       </c>
@@ -2610,28 +4310,28 @@
         <v>47</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="G13" s="3" t="s">
         <v>15</v>
       </c>
@@ -2639,28 +4339,28 @@
         <v>47</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>15</v>
       </c>
@@ -2668,28 +4368,28 @@
         <v>47</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="G15" s="3" t="s">
         <v>15</v>
       </c>
@@ -2697,28 +4397,28 @@
         <v>47</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="G16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2726,28 +4426,28 @@
         <v>47</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="G17" s="3" t="s">
         <v>15</v>
       </c>
@@ -2755,28 +4455,28 @@
         <v>47</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="G18" s="3" t="s">
         <v>15</v>
       </c>
@@ -2784,36 +4484,36 @@
         <v>47</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="20" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2842,7 +4542,7 @@
         <v>47</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2871,7 +4571,7 @@
         <v>47</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2900,7 +4600,7 @@
         <v>47</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2929,7 +4629,7 @@
         <v>47</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2958,7 +4658,7 @@
         <v>47</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2987,7 +4687,7 @@
         <v>47</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3016,7 +4716,7 @@
         <v>47</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3045,7 +4745,7 @@
         <v>47</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3074,28 +4774,28 @@
         <v>47</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>128</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="G29" s="3" t="s">
         <v>15</v>
       </c>
@@ -3103,28 +4803,28 @@
         <v>47</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>150</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="G30" s="3" t="s">
         <v>15</v>
       </c>
@@ -3132,28 +4832,28 @@
         <v>47</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="G31" s="3" t="s">
         <v>15</v>
       </c>
@@ -3161,28 +4861,28 @@
         <v>47</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>15</v>
       </c>
@@ -3190,28 +4890,28 @@
         <v>47</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="G33" s="3" t="s">
         <v>15</v>
       </c>
@@ -3219,28 +4919,28 @@
         <v>47</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="G34" s="3" t="s">
         <v>15</v>
       </c>
@@ -3248,28 +4948,28 @@
         <v>47</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="G35" s="3" t="s">
         <v>15</v>
       </c>
@@ -3277,28 +4977,28 @@
         <v>47</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>150</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="G36" s="3" t="s">
         <v>15</v>
       </c>
@@ -3306,28 +5006,28 @@
         <v>47</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>150</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="G37" s="3" t="s">
         <v>15</v>
       </c>
@@ -3335,28 +5035,28 @@
         <v>47</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="G38" s="3" t="s">
         <v>15</v>
       </c>
@@ -3364,28 +5064,28 @@
         <v>47</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="G39" s="3" t="s">
         <v>15</v>
       </c>
@@ -3393,28 +5093,28 @@
         <v>47</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="G40" s="3" t="s">
         <v>15</v>
       </c>
@@ -3422,28 +5122,28 @@
         <v>47</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="F41" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="G41" s="3" t="s">
         <v>15</v>
       </c>
@@ -3451,28 +5151,28 @@
         <v>47</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="G42" s="3" t="s">
         <v>15</v>
       </c>
@@ -3480,28 +5180,28 @@
         <v>47</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="E43" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="F43" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>15</v>
       </c>
@@ -3509,28 +5209,28 @@
         <v>47</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>15</v>
       </c>
@@ -3538,28 +5238,28 @@
         <v>47</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>15</v>
       </c>
@@ -3567,28 +5267,28 @@
         <v>47</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="G46" s="3" t="s">
         <v>15</v>
       </c>
@@ -3596,57 +5296,57 @@
         <v>47</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="G47" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I47" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="48" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="F48" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F48" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>15</v>
       </c>
@@ -3654,28 +5354,28 @@
         <v>47</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="F49" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>15</v>
       </c>
@@ -3683,28 +5383,28 @@
         <v>47</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>272</v>
-      </c>
       <c r="G50" s="3" t="s">
         <v>15</v>
       </c>
@@ -3712,28 +5412,28 @@
         <v>47</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>277</v>
-      </c>
       <c r="G51" s="3" t="s">
         <v>15</v>
       </c>
@@ -3741,28 +5441,28 @@
         <v>47</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="F52" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>15</v>
       </c>
@@ -3770,28 +5470,28 @@
         <v>47</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
     </row>
     <row r="53" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>287</v>
-      </c>
       <c r="G53" s="3" t="s">
         <v>15</v>
       </c>
@@ -3799,28 +5499,28 @@
         <v>47</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="G54" s="3" t="s">
         <v>15</v>
       </c>
@@ -3828,28 +5528,28 @@
         <v>47</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="E55" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D55" s="2" t="s">
+      <c r="F55" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>298</v>
-      </c>
       <c r="G55" s="3" t="s">
         <v>15</v>
       </c>
@@ -3857,28 +5557,28 @@
         <v>47</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
     </row>
     <row r="56" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>150</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="G56" s="3" t="s">
         <v>15</v>
       </c>
@@ -3886,28 +5586,28 @@
         <v>47</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
     </row>
     <row r="57" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D57" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>15</v>
       </c>
@@ -3915,28 +5615,28 @@
         <v>47</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
     </row>
     <row r="58" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="G58" s="3" t="s">
         <v>15</v>
       </c>
@@ -3944,28 +5644,28 @@
         <v>47</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
     </row>
     <row r="59" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="E59" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D59" s="2" t="s">
+      <c r="F59" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>15</v>
       </c>
@@ -3973,28 +5673,28 @@
         <v>47</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>319</v>
+        <v>256</v>
       </c>
     </row>
     <row r="60" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="G60" s="3" t="s">
         <v>15</v>
       </c>
@@ -4002,28 +5702,28 @@
         <v>47</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>319</v>
+        <v>256</v>
       </c>
     </row>
     <row r="61" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="F61" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>329</v>
-      </c>
       <c r="G61" s="3" t="s">
         <v>15</v>
       </c>
@@ -4031,27 +5731,27 @@
         <v>47</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>319</v>
+        <v>256</v>
       </c>
     </row>
     <row r="62" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>15</v>
@@ -4060,27 +5760,27 @@
         <v>47</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>319</v>
+        <v>256</v>
       </c>
     </row>
     <row r="63" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>139</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>15</v>
@@ -4089,27 +5789,27 @@
         <v>47</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>319</v>
+        <v>256</v>
       </c>
     </row>
     <row r="64" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>15</v>
@@ -4118,27 +5818,27 @@
         <v>47</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>319</v>
+        <v>256</v>
       </c>
     </row>
     <row r="65" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>15</v>
@@ -4147,28 +5847,28 @@
         <v>47</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>319</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="E66" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="F66" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>355</v>
-      </c>
       <c r="G66" s="3" t="s">
         <v>15</v>
       </c>
@@ -4176,57 +5876,57 @@
         <v>47</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>319</v>
+        <v>256</v>
       </c>
     </row>
     <row r="67" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="F67" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D67" s="2" t="s">
+      <c r="G67" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I67" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="68" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D68" s="2" t="s">
+      <c r="F68" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>365</v>
-      </c>
       <c r="G68" s="3" t="s">
         <v>15</v>
       </c>
@@ -4234,28 +5934,28 @@
         <v>47</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="69" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="E69" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D69" s="2" t="s">
+      <c r="F69" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>370</v>
-      </c>
       <c r="G69" s="3" t="s">
         <v>15</v>
       </c>
@@ -4263,28 +5963,28 @@
         <v>47</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="70" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D70" s="2" t="s">
+      <c r="F70" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="G70" s="3" t="s">
         <v>15</v>
       </c>
@@ -4292,28 +5992,28 @@
         <v>47</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="71" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="E71" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D71" s="2" t="s">
+      <c r="F71" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="G71" s="3" t="s">
         <v>15</v>
       </c>
@@ -4321,28 +6021,28 @@
         <v>47</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="72" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="E72" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D72" s="2" t="s">
+      <c r="F72" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>385</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>15</v>
       </c>
@@ -4350,28 +6050,28 @@
         <v>47</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="73" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D73" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>390</v>
-      </c>
       <c r="G73" s="3" t="s">
         <v>15</v>
       </c>
@@ -4379,28 +6079,28 @@
         <v>47</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="74" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>395</v>
-      </c>
       <c r="G74" s="3" t="s">
         <v>15</v>
       </c>
@@ -4408,28 +6108,28 @@
         <v>47</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="75" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="F75" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="G75" s="3" t="s">
         <v>15</v>
       </c>
@@ -4437,28 +6137,28 @@
         <v>47</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="76" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D76" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="G76" s="3" t="s">
         <v>15</v>
       </c>
@@ -4466,28 +6166,28 @@
         <v>47</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="77" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D77" s="2" t="s">
+      <c r="F77" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>411</v>
-      </c>
       <c r="G77" s="3" t="s">
         <v>15</v>
       </c>
@@ -4495,28 +6195,28 @@
         <v>47</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="78" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="E78" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D78" s="2" t="s">
+      <c r="F78" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>416</v>
-      </c>
       <c r="G78" s="3" t="s">
         <v>15</v>
       </c>
@@ -4524,28 +6224,28 @@
         <v>47</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="79" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="E79" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D79" s="2" t="s">
+      <c r="F79" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>421</v>
-      </c>
       <c r="G79" s="3" t="s">
         <v>15</v>
       </c>
@@ -4553,28 +6253,28 @@
         <v>47</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="80" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="E80" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D80" s="2" t="s">
+      <c r="F80" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>426</v>
-      </c>
       <c r="G80" s="3" t="s">
         <v>15</v>
       </c>
@@ -4582,28 +6282,28 @@
         <v>47</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="81" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="E81" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D81" s="2" t="s">
+      <c r="F81" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="G81" s="3" t="s">
         <v>15</v>
       </c>
@@ -4611,28 +6311,28 @@
         <v>47</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="82" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="E82" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D82" s="2" t="s">
+      <c r="F82" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>436</v>
-      </c>
       <c r="G82" s="3" t="s">
         <v>15</v>
       </c>
@@ -4640,28 +6340,28 @@
         <v>47</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="83" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D83" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>441</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>15</v>
       </c>
@@ -4669,28 +6369,28 @@
         <v>47</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="84" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D84" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F84" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>446</v>
-      </c>
       <c r="G84" s="3" t="s">
         <v>15</v>
       </c>
@@ -4698,28 +6398,28 @@
         <v>47</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="85" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="F85" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>452</v>
-      </c>
       <c r="G85" s="3" t="s">
         <v>15</v>
       </c>
@@ -4727,28 +6427,28 @@
         <v>47</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="86" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="E86" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="D86" s="2" t="s">
+      <c r="F86" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>457</v>
-      </c>
       <c r="G86" s="3" t="s">
         <v>15</v>
       </c>
@@ -4756,28 +6456,28 @@
         <v>47</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>319</v>
+        <v>358</v>
       </c>
     </row>
     <row r="87" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="E87" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="D87" s="2" t="s">
+      <c r="F87" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="G87" s="3" t="s">
         <v>15</v>
       </c>
@@ -4785,28 +6485,28 @@
         <v>47</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="E88" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>469</v>
-      </c>
       <c r="G88" s="3" t="s">
         <v>15</v>
       </c>
@@ -4814,28 +6514,28 @@
         <v>47</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="F89" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>474</v>
-      </c>
       <c r="G89" s="3" t="s">
         <v>15</v>
       </c>
@@ -4843,28 +6543,28 @@
         <v>47</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="90" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="F90" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="G90" s="3" t="s">
         <v>15</v>
       </c>
@@ -4872,28 +6572,28 @@
         <v>47</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="91" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="F91" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>484</v>
-      </c>
       <c r="G91" s="3" t="s">
         <v>15</v>
       </c>
@@ -4901,28 +6601,28 @@
         <v>47</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="F92" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="G92" s="3" t="s">
         <v>15</v>
       </c>
@@ -4930,28 +6630,28 @@
         <v>47</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="F93" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>494</v>
-      </c>
       <c r="G93" s="3" t="s">
         <v>15</v>
       </c>
@@ -4959,28 +6659,28 @@
         <v>47</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="F94" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="G94" s="3" t="s">
         <v>15</v>
       </c>
@@ -4988,28 +6688,28 @@
         <v>47</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="F95" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="G95" s="3" t="s">
         <v>15</v>
       </c>
@@ -5017,28 +6717,28 @@
         <v>47</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="E96" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="F96" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>15</v>
       </c>
@@ -5046,28 +6746,28 @@
         <v>47</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="F97" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>515</v>
-      </c>
       <c r="G97" s="3" t="s">
         <v>15</v>
       </c>
@@ -5075,28 +6775,28 @@
         <v>47</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="98" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="F98" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>520</v>
-      </c>
       <c r="G98" s="3" t="s">
         <v>15</v>
       </c>
@@ -5104,28 +6804,28 @@
         <v>47</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="99" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="F99" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>525</v>
-      </c>
       <c r="G99" s="3" t="s">
         <v>15</v>
       </c>
@@ -5133,28 +6833,28 @@
         <v>47</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="100" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="E100" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="C100" s="2" t="s">
+      <c r="F100" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>15</v>
       </c>
@@ -5162,28 +6862,28 @@
         <v>47</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="101" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>536</v>
-      </c>
       <c r="G101" s="3" t="s">
         <v>15</v>
       </c>
@@ -5191,57 +6891,57 @@
         <v>47</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>463</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="F102" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="D102" s="2" t="s">
+      <c r="G102" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I102" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="103" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="E103" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="D103" s="2" t="s">
+      <c r="F103" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="E103" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>546</v>
-      </c>
       <c r="G103" s="3" t="s">
         <v>15</v>
       </c>
@@ -5249,28 +6949,28 @@
         <v>47</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
     </row>
     <row r="104" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="E104" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="D104" s="2" t="s">
+      <c r="F104" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>551</v>
-      </c>
       <c r="G104" s="3" t="s">
         <v>15</v>
       </c>
@@ -5278,28 +6978,28 @@
         <v>47</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
     </row>
     <row r="105" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="E105" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="D105" s="2" t="s">
+      <c r="F105" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>556</v>
-      </c>
       <c r="G105" s="3" t="s">
         <v>15</v>
       </c>
@@ -5307,39 +7007,2939 @@
         <v>47</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>463</v>
+        <v>539</v>
       </c>
     </row>
     <row r="106" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="E106" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D106" s="2" t="s">
+      <c r="F106" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="E106" s="2" t="s">
+      <c r="G106" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="107" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="F106" s="2" t="s">
+      <c r="B107" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="G106" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I106" s="2" t="s">
+      <c r="C107" s="2" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="107" spans="7:7" x14ac:dyDescent="0.25"/>
+      <c r="D107" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="108" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="109" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="110" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="111" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="112" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="113" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="114" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="115" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="116" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="117" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="118" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="119" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="120" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="121" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="122" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="123" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="124" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="125" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="126" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="127" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="128" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="129" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="130" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="131" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="132" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="133" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="134" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="135" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="136" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="137" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="138" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="139" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="140" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="141" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="142" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="143" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="144" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="145" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="146" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="147" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="148" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="149" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="150" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="151" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="152" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="153" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="154" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="155" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="156" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="157" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="158" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="159" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="160" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="161" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="162" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="163" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="164" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="165" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="166" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="167" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="168" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="169" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="170" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="171" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="172" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="173" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="174" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="175" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="176" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="177" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="178" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="179" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I179" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="180" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="181" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I181" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="182" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="183" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I183" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="184" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I184" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="185" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I185" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="186" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I186" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="187" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I187" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="188" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I188" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="189" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I189" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="190" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I190" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="191" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H191" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I191" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="192" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I192" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="193" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I193" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="194" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I194" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="195" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I195" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="196" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I196" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="197" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I197" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="198" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I198" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="199" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I199" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="200" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I200" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="201" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I201" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="202" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I202" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="203" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I203" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="204" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I204" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="205" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I205" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="206" ht="52" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I206" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="207" spans="7:7" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5357,18 +9957,18 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>562</v>
+        <v>1062</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>563</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>564</v>
+        <v>1064</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5376,12 +9976,12 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>106</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>565</v>
+        <v>1065</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5389,7 +9989,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>566</v>
+        <v>1066</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5397,10 +9997,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>567</v>
+        <v>1067</v>
       </c>
       <c r="B6">
-        <v>101</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
